--- a/research/traditional_assets/database/data/china/china_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/china/china_insurance_general.xlsx
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09910000000000001</v>
+        <v>0.23275</v>
       </c>
       <c r="E2">
-        <v>0.191</v>
+        <v>0.115</v>
       </c>
       <c r="F2">
-        <v>0.0795</v>
+        <v>0.0591</v>
       </c>
       <c r="G2">
-        <v>0.09154096688259299</v>
+        <v>0.09994373724230596</v>
       </c>
       <c r="H2">
-        <v>0.09154096688259299</v>
+        <v>0.09994373724230596</v>
       </c>
       <c r="I2">
-        <v>0.09409088679893604</v>
+        <v>0.0666274661384843</v>
       </c>
       <c r="J2">
-        <v>0.08352435463410057</v>
+        <v>0.06606338317704508</v>
       </c>
       <c r="K2">
-        <v>4286.312</v>
+        <v>3395.76</v>
       </c>
       <c r="L2">
-        <v>0.06456313318496743</v>
+        <v>0.05149725662186878</v>
       </c>
       <c r="M2">
-        <v>2403.8</v>
+        <v>1836.4</v>
       </c>
       <c r="N2">
-        <v>0.06536724409817106</v>
+        <v>0.05310851384656139</v>
       </c>
       <c r="O2">
-        <v>0.5608084525811468</v>
+        <v>0.5407920465521709</v>
       </c>
       <c r="P2">
-        <v>2403.8</v>
+        <v>1836.4</v>
       </c>
       <c r="Q2">
-        <v>0.06536724409817106</v>
+        <v>0.05310851384656139</v>
       </c>
       <c r="R2">
-        <v>0.5608084525811468</v>
+        <v>0.5407920465521709</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3392.929</v>
+        <v>4237</v>
       </c>
       <c r="V2">
-        <v>0.09226492143720917</v>
+        <v>0.1225336381876937</v>
       </c>
       <c r="W2">
-        <v>0.06366120218579235</v>
+        <v>-0.01243771334405776</v>
       </c>
       <c r="X2">
-        <v>0.04928442452812504</v>
+        <v>0.1003292968774003</v>
       </c>
       <c r="Y2">
-        <v>0.01437677765766731</v>
+        <v>-0.1127670102214581</v>
       </c>
       <c r="Z2">
-        <v>1.500735074056727</v>
+        <v>1.325606781141122</v>
       </c>
       <c r="AA2">
-        <v>0.2479965042454344</v>
+        <v>0.01682688738640967</v>
       </c>
       <c r="AB2">
-        <v>0.04881506315294062</v>
+        <v>0.08173960981974926</v>
       </c>
       <c r="AC2">
-        <v>0.1991059583620942</v>
+        <v>-0.06491272243333959</v>
       </c>
       <c r="AD2">
-        <v>16249.9</v>
+        <v>20460.3</v>
       </c>
       <c r="AE2">
-        <v>0.3158793064966189</v>
+        <v>0.604531743310384</v>
       </c>
       <c r="AF2">
-        <v>16250.2158793065</v>
+        <v>20460.90453174331</v>
       </c>
       <c r="AG2">
-        <v>12857.2868793065</v>
+        <v>16223.90453174331</v>
       </c>
       <c r="AH2">
-        <v>0.30646914994839</v>
+        <v>0.3717517281706316</v>
       </c>
       <c r="AI2">
-        <v>0.3164110560283178</v>
+        <v>0.3714268597032732</v>
       </c>
       <c r="AJ2">
-        <v>0.2590572856542835</v>
+        <v>0.3193545920982547</v>
       </c>
       <c r="AK2">
-        <v>0.2680556123792409</v>
+        <v>0.3190522590010357</v>
       </c>
       <c r="AL2">
-        <v>1074.601</v>
+        <v>1099.501</v>
       </c>
       <c r="AM2">
-        <v>1074.503</v>
+        <v>1099.112</v>
       </c>
       <c r="AN2">
-        <v>2.464115434737842</v>
+        <v>4.345778730464992</v>
       </c>
       <c r="AO2">
-        <v>5.812859842862607</v>
+        <v>3.995567079975371</v>
       </c>
       <c r="AP2">
-        <v>1.94966363166244</v>
+        <v>3.445966053241872</v>
       </c>
       <c r="AQ2">
-        <v>5.813390004495101</v>
+        <v>3.996981199368217</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>QDM International Inc. (OTCPK:QDMI)</t>
+          <t>China Pacific Insurance (Group) Co., Ltd. (SHSE:601601)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,113 +724,125 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0735</v>
+      </c>
+      <c r="E3">
+        <v>0.115</v>
+      </c>
+      <c r="F3">
+        <v>0.0591</v>
+      </c>
       <c r="G3">
-        <v>-3.609195402298851</v>
+        <v>0.1025611470250159</v>
       </c>
       <c r="H3">
-        <v>-3.609195402298851</v>
+        <v>0.1025611470250159</v>
       </c>
       <c r="I3">
-        <v>-4.075616013607973</v>
+        <v>0.06965910073289981</v>
       </c>
       <c r="J3">
-        <v>-4.075616013607973</v>
+        <v>0.06788985236837683</v>
       </c>
       <c r="K3">
-        <v>-0.354</v>
+        <v>3432.5</v>
       </c>
       <c r="L3">
-        <v>-4.068965517241379</v>
+        <v>0.05495147620557055</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1836.4</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.06016919719795811</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.5350036416605972</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1836.4</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.06016919719795811</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.5350036416605972</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.029</v>
+        <v>3729.2</v>
       </c>
       <c r="V3">
-        <v>0.004044630404463041</v>
+        <v>0.1221863266121898</v>
       </c>
       <c r="W3">
-        <v>-6.679245283018868</v>
+        <v>0.1002137113961894</v>
       </c>
       <c r="X3">
-        <v>0.04882356311858348</v>
+        <v>0.1020101109561516</v>
       </c>
       <c r="Y3">
-        <v>-6.728068846137451</v>
+        <v>-0.00179639955996222</v>
       </c>
       <c r="Z3">
-        <v>-3.209499045212139</v>
+        <v>1.331458985678079</v>
       </c>
       <c r="AA3">
-        <v>13.0806857043261</v>
+        <v>0.09039255397223357</v>
       </c>
       <c r="AB3">
-        <v>0.04881506315294062</v>
+        <v>0.07953758455893725</v>
       </c>
       <c r="AC3">
-        <v>13.03187064117316</v>
+        <v>0.01085496941329632</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>18245.6</v>
       </c>
       <c r="AE3">
-        <v>0.002892965919468123</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.002892965919468123</v>
+        <v>18245.6</v>
       </c>
       <c r="AG3">
-        <v>-0.02610703408053188</v>
+        <v>14516.4</v>
       </c>
       <c r="AH3">
-        <v>0.0004033192650738633</v>
+        <v>0.3741443868909203</v>
       </c>
       <c r="AI3">
-        <v>-0.005951294090899443</v>
+        <v>0.3634357240887515</v>
       </c>
       <c r="AJ3">
-        <v>-0.003654454819672921</v>
+        <v>0.3223216466460909</v>
       </c>
       <c r="AK3">
-        <v>0.05068273650569156</v>
+        <v>0.3123559675430725</v>
       </c>
       <c r="AL3">
-        <v>0.001</v>
+        <v>1035.1</v>
       </c>
       <c r="AM3">
-        <v>0.001</v>
+        <v>1035.1</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>3.906227921813783</v>
       </c>
       <c r="AO3">
-        <v>-357</v>
+        <v>4.203651821080089</v>
       </c>
       <c r="AP3">
-        <v>0.07395760362756906</v>
+        <v>3.107837889914149</v>
       </c>
       <c r="AQ3">
-        <v>-357</v>
+        <v>4.203651821080089</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tian Ruixiang Holdings Ltd (NasdaqCM:TIRX)</t>
+          <t>ZhongAn Online P &amp; C Insurance Co., Ltd. (SEHK:6060)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -849,23 +861,26 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.392</v>
+      </c>
       <c r="G4">
-        <v>0.1363636363636364</v>
+        <v>0.05359352963186828</v>
       </c>
       <c r="H4">
-        <v>0.1363636363636364</v>
+        <v>0.05359352963186828</v>
       </c>
       <c r="I4">
-        <v>0.143158548297744</v>
+        <v>0.01370060156002648</v>
       </c>
       <c r="J4">
-        <v>0.1123095681931796</v>
+        <v>0.01370060156002648</v>
       </c>
       <c r="K4">
-        <v>0.466</v>
+        <v>-31.7</v>
       </c>
       <c r="L4">
-        <v>0.1114832535885168</v>
+        <v>-0.00912414011455545</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -874,7 +889,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -883,76 +898,79 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>18.2</v>
+        <v>478.8</v>
       </c>
       <c r="V4">
-        <v>1.083333333333333</v>
+        <v>0.1181405448085274</v>
       </c>
       <c r="W4">
-        <v>0.06366120218579235</v>
+        <v>-0.01243771334405776</v>
       </c>
       <c r="X4">
-        <v>0.04928442452812504</v>
+        <v>0.1003292968774003</v>
       </c>
       <c r="Y4">
-        <v>0.01437677765766731</v>
+        <v>-0.1127670102214581</v>
       </c>
       <c r="Z4">
-        <v>2.20815116855284</v>
+        <v>1.228186026189141</v>
       </c>
       <c r="AA4">
-        <v>0.2479965042454344</v>
+        <v>0.01682688738640967</v>
       </c>
       <c r="AB4">
-        <v>0.04889054588334019</v>
+        <v>0.08173960981974926</v>
       </c>
       <c r="AC4">
-        <v>0.1991059583620942</v>
+        <v>-0.06491272243333959</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2214.7</v>
       </c>
       <c r="AE4">
-        <v>0.3129863405771508</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.3129863405771508</v>
+        <v>2214.7</v>
       </c>
       <c r="AG4">
-        <v>-17.88701365942285</v>
+        <v>1735.9</v>
       </c>
       <c r="AH4">
-        <v>0.01828940515396888</v>
+        <v>0.3533625847626645</v>
       </c>
       <c r="AI4">
-        <v>0.01672562224333338</v>
+        <v>0.45696894666254</v>
       </c>
       <c r="AJ4">
-        <v>16.45518757227025</v>
+        <v>0.2998773472454955</v>
       </c>
       <c r="AK4">
-        <v>-34.86840144573546</v>
+        <v>0.3974403003869313</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AM4">
-        <v>-0.098</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>52.23349056603773</v>
+      </c>
+      <c r="AO4">
+        <v>0.7391304347826086</v>
       </c>
       <c r="AP4">
-        <v>-26.65724837469873</v>
+        <v>40.94103773584906</v>
       </c>
       <c r="AQ4">
-        <v>-4.714285714285714</v>
+        <v>0.7391304347826086</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>China Pacific Insurance (Group) Co., Ltd. (SHSE:601601)</t>
+          <t>Tian Ruixiang Holdings Ltd (NasdaqCM:TIRX)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -971,125 +989,113 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.09910000000000001</v>
-      </c>
-      <c r="E5">
-        <v>0.191</v>
-      </c>
-      <c r="F5">
-        <v>0.0795</v>
-      </c>
       <c r="G5">
-        <v>0.09154299452287559</v>
+        <v>-1.071428571428571</v>
       </c>
       <c r="H5">
-        <v>0.09154299452287559</v>
+        <v>-1.071428571428571</v>
       </c>
       <c r="I5">
-        <v>0.0940932617511132</v>
+        <v>-2.545193499362894</v>
       </c>
       <c r="J5">
-        <v>0.08266885418992216</v>
+        <v>-2.545193499362894</v>
       </c>
       <c r="K5">
-        <v>4286.2</v>
+        <v>-5.04</v>
       </c>
       <c r="L5">
-        <v>0.06456559594608437</v>
+        <v>-2.4</v>
       </c>
       <c r="M5">
-        <v>2403.8</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.06540987978165867</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.5608231067145724</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>2403.8</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.06540987978165867</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.5608231067145724</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>3374.7</v>
+        <v>29</v>
       </c>
       <c r="V5">
-        <v>0.09182907117861865</v>
+        <v>5.967078189300411</v>
       </c>
       <c r="W5">
-        <v>0.1435595479726426</v>
+        <v>-0.2739130434782609</v>
       </c>
       <c r="X5">
-        <v>0.05999380448562235</v>
+        <v>0.08651405583827518</v>
       </c>
       <c r="Y5">
-        <v>0.08356574348702021</v>
+        <v>-0.360427099316536</v>
       </c>
       <c r="Z5">
-        <v>1.500701915403935</v>
+        <v>2.610213975348184</v>
       </c>
       <c r="AA5">
-        <v>0.1240613078270648</v>
+        <v>-6.643499642002374</v>
       </c>
       <c r="AB5">
-        <v>0.04834480443380177</v>
+        <v>0.08524263538609805</v>
       </c>
       <c r="AC5">
-        <v>0.07571650339326302</v>
+        <v>-6.728742277388473</v>
       </c>
       <c r="AD5">
-        <v>16249.9</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>0.604531743310384</v>
       </c>
       <c r="AF5">
-        <v>16249.9</v>
+        <v>0.604531743310384</v>
       </c>
       <c r="AG5">
-        <v>12875.2</v>
+        <v>-28.39546825668961</v>
       </c>
       <c r="AH5">
-        <v>0.3066036222846544</v>
+        <v>0.1106282791842951</v>
       </c>
       <c r="AI5">
-        <v>0.3165172371478602</v>
+        <v>0.01603339745540379</v>
       </c>
       <c r="AJ5">
-        <v>0.2594498740554156</v>
+        <v>1.206496847523678</v>
       </c>
       <c r="AK5">
-        <v>0.2684290628583342</v>
+        <v>-3.26214770582141</v>
       </c>
       <c r="AL5">
-        <v>1074.6</v>
+        <v>0.001</v>
       </c>
       <c r="AM5">
-        <v>1074.6</v>
+        <v>-0.388</v>
       </c>
       <c r="AN5">
-        <v>2.46423426292404</v>
+        <v>-0</v>
       </c>
       <c r="AO5">
-        <v>5.812767541410758</v>
+        <v>-5670</v>
       </c>
       <c r="AP5">
-        <v>1.952474106425246</v>
+        <v>5.446004652222787</v>
       </c>
       <c r="AQ5">
-        <v>5.812767541410758</v>
+        <v>14.61340206185567</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/china/china_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/china/china_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.23275</v>
+        <v>0.1619</v>
       </c>
       <c r="E2">
-        <v>0.115</v>
+        <v>0.00825</v>
       </c>
       <c r="F2">
-        <v>0.0591</v>
+        <v>0.09820000000000001</v>
       </c>
       <c r="G2">
-        <v>0.09994373724230596</v>
+        <v>0.07237937261850866</v>
       </c>
       <c r="H2">
-        <v>0.09994373724230596</v>
+        <v>0.07227007744106778</v>
       </c>
       <c r="I2">
-        <v>0.0666274661384843</v>
+        <v>0.04503455836784698</v>
       </c>
       <c r="J2">
-        <v>0.06606338317704508</v>
+        <v>0.04503455836784698</v>
       </c>
       <c r="K2">
-        <v>3395.76</v>
+        <v>2305.13</v>
       </c>
       <c r="L2">
-        <v>0.05149725662186878</v>
+        <v>0.03479828623954091</v>
       </c>
       <c r="M2">
-        <v>1836.4</v>
+        <v>2100.8</v>
       </c>
       <c r="N2">
-        <v>0.05310851384656139</v>
+        <v>0.06483338301999873</v>
       </c>
       <c r="O2">
-        <v>0.5407920465521709</v>
+        <v>0.9113585784749669</v>
       </c>
       <c r="P2">
-        <v>1836.4</v>
+        <v>2100.8</v>
       </c>
       <c r="Q2">
-        <v>0.05310851384656139</v>
+        <v>0.06483338301999873</v>
       </c>
       <c r="R2">
-        <v>0.5407920465521709</v>
+        <v>0.9113585784749669</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4237</v>
+        <v>4350.9</v>
       </c>
       <c r="V2">
-        <v>0.1225336381876937</v>
+        <v>0.1342743555701221</v>
       </c>
       <c r="W2">
-        <v>-0.01243771334405776</v>
+        <v>-0.05033699480063234</v>
       </c>
       <c r="X2">
-        <v>0.1003292968774003</v>
+        <v>0.08159951777453131</v>
       </c>
       <c r="Y2">
-        <v>-0.1127670102214581</v>
+        <v>-0.1319365125751636</v>
       </c>
       <c r="Z2">
-        <v>1.325606781141122</v>
+        <v>1.333786540620028</v>
       </c>
       <c r="AA2">
-        <v>0.01682688738640967</v>
+        <v>-0.1774942966610899</v>
       </c>
       <c r="AB2">
-        <v>0.08173960981974926</v>
+        <v>0.07315602359349746</v>
       </c>
       <c r="AC2">
-        <v>-0.06491272243333959</v>
+        <v>-0.2506503202545873</v>
       </c>
       <c r="AD2">
-        <v>20460.3</v>
+        <v>16987.69</v>
       </c>
       <c r="AE2">
-        <v>0.604531743310384</v>
+        <v>2.167064126540449</v>
       </c>
       <c r="AF2">
-        <v>20460.90453174331</v>
+        <v>16989.85706412654</v>
       </c>
       <c r="AG2">
-        <v>16223.90453174331</v>
+        <v>12638.95706412654</v>
       </c>
       <c r="AH2">
-        <v>0.3717517281706316</v>
+        <v>0.3439735507434944</v>
       </c>
       <c r="AI2">
-        <v>0.3714268597032732</v>
+        <v>0.320416088092862</v>
       </c>
       <c r="AJ2">
-        <v>0.3193545920982547</v>
+        <v>0.2806037093350504</v>
       </c>
       <c r="AK2">
-        <v>0.3190522590010357</v>
+        <v>0.2596683660146619</v>
       </c>
       <c r="AL2">
-        <v>1099.501</v>
+        <v>1083.779</v>
       </c>
       <c r="AM2">
-        <v>1099.112</v>
+        <v>1082.971</v>
       </c>
       <c r="AN2">
-        <v>4.345778730464992</v>
+        <v>5.116603029236071</v>
       </c>
       <c r="AO2">
-        <v>3.995567079975371</v>
+        <v>2.751741821902804</v>
       </c>
       <c r="AP2">
-        <v>3.445966053241872</v>
+        <v>3.806787503227013</v>
       </c>
       <c r="AQ2">
-        <v>3.996981199368217</v>
+        <v>2.753794884627566</v>
       </c>
     </row>
     <row r="3">
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0735</v>
+        <v>0.0548</v>
       </c>
       <c r="E3">
-        <v>0.115</v>
+        <v>0.00825</v>
       </c>
       <c r="F3">
-        <v>0.0591</v>
+        <v>0.09820000000000001</v>
       </c>
       <c r="G3">
-        <v>0.1025611470250159</v>
+        <v>0.07861935954351804</v>
       </c>
       <c r="H3">
-        <v>0.1025611470250159</v>
+        <v>0.07861935954351804</v>
       </c>
       <c r="I3">
-        <v>0.06965910073289981</v>
+        <v>0.04798785870552563</v>
       </c>
       <c r="J3">
-        <v>0.06788985236837683</v>
+        <v>0.04798785870552563</v>
       </c>
       <c r="K3">
-        <v>3432.5</v>
+        <v>2349.2</v>
       </c>
       <c r="L3">
-        <v>0.05495147620557055</v>
+        <v>0.03756892647416296</v>
       </c>
       <c r="M3">
-        <v>1836.4</v>
+        <v>2100.8</v>
       </c>
       <c r="N3">
-        <v>0.06016919719795811</v>
+        <v>0.07357133351544061</v>
       </c>
       <c r="O3">
-        <v>0.5350036416605972</v>
+        <v>0.8942618763834498</v>
       </c>
       <c r="P3">
-        <v>1836.4</v>
+        <v>2100.8</v>
       </c>
       <c r="Q3">
-        <v>0.06016919719795811</v>
+        <v>0.07357133351544061</v>
       </c>
       <c r="R3">
-        <v>0.5350036416605972</v>
+        <v>0.8942618763834498</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,73 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3729.2</v>
+        <v>3857.1</v>
       </c>
       <c r="V3">
-        <v>0.1221863266121898</v>
+        <v>0.135078060977916</v>
       </c>
       <c r="W3">
-        <v>0.1002137113961894</v>
+        <v>0.07533592021293653</v>
       </c>
       <c r="X3">
-        <v>0.1020101109561516</v>
+        <v>0.08777963602640382</v>
       </c>
       <c r="Y3">
-        <v>-0.00179639955996222</v>
+        <v>-0.01244371581346729</v>
       </c>
       <c r="Z3">
-        <v>1.331458985678079</v>
+        <v>1.374098205750827</v>
       </c>
       <c r="AA3">
-        <v>0.09039255397223357</v>
+        <v>0.06594003054508696</v>
       </c>
       <c r="AB3">
-        <v>0.07953758455893725</v>
+        <v>0.07107688422009895</v>
       </c>
       <c r="AC3">
-        <v>0.01085496941329632</v>
+        <v>-0.005136853675011988</v>
       </c>
       <c r="AD3">
-        <v>18245.6</v>
+        <v>15125.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18245.6</v>
+        <v>15125.3</v>
       </c>
       <c r="AG3">
-        <v>14516.4</v>
+        <v>11268.2</v>
       </c>
       <c r="AH3">
-        <v>0.3741443868909203</v>
+        <v>0.3462759759065383</v>
       </c>
       <c r="AI3">
-        <v>0.3634357240887515</v>
+        <v>0.3110883041344615</v>
       </c>
       <c r="AJ3">
-        <v>0.3223216466460909</v>
+        <v>0.282958506182388</v>
       </c>
       <c r="AK3">
-        <v>0.3123559675430725</v>
+        <v>0.2517274118422375</v>
       </c>
       <c r="AL3">
-        <v>1035.1</v>
+        <v>1022.4</v>
       </c>
       <c r="AM3">
-        <v>1035.1</v>
+        <v>1022.4</v>
       </c>
       <c r="AN3">
-        <v>3.906227921813783</v>
+        <v>4.524875100966285</v>
       </c>
       <c r="AO3">
-        <v>4.203651821080089</v>
+        <v>2.93495696400626</v>
       </c>
       <c r="AP3">
-        <v>3.107837889914149</v>
+        <v>3.370987525054597</v>
       </c>
       <c r="AQ3">
-        <v>4.203651821080089</v>
+        <v>2.93495696400626</v>
       </c>
     </row>
     <row r="4">
@@ -862,25 +862,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.392</v>
+        <v>0.269</v>
       </c>
       <c r="G4">
-        <v>0.05359352963186828</v>
+        <v>-0.032353206729467</v>
       </c>
       <c r="H4">
-        <v>0.05359352963186828</v>
+        <v>-0.032353206729467</v>
       </c>
       <c r="I4">
-        <v>0.01370060156002648</v>
+        <v>0.0004123152857615795</v>
       </c>
       <c r="J4">
-        <v>0.01370060156002648</v>
+        <v>0.0004123152857615795</v>
       </c>
       <c r="K4">
-        <v>-31.7</v>
+        <v>-68.7</v>
       </c>
       <c r="L4">
-        <v>-0.00912414011455545</v>
+        <v>-0.02067595630059891</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -904,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>478.8</v>
+        <v>441.2</v>
       </c>
       <c r="V4">
-        <v>0.1181405448085274</v>
+        <v>0.1314425311326938</v>
       </c>
       <c r="W4">
-        <v>-0.01243771334405776</v>
+        <v>-0.02870633461474177</v>
       </c>
       <c r="X4">
-        <v>0.1003292968774003</v>
+        <v>0.0883726864346773</v>
       </c>
       <c r="Y4">
-        <v>-0.1127670102214581</v>
+        <v>-0.1170790210494191</v>
       </c>
       <c r="Z4">
-        <v>1.228186026189141</v>
+        <v>0.8047959804525673</v>
       </c>
       <c r="AA4">
-        <v>0.01682688738640967</v>
+        <v>0.0003318296846600708</v>
       </c>
       <c r="AB4">
-        <v>0.08173960981974926</v>
+        <v>0.07255152925674307</v>
       </c>
       <c r="AC4">
-        <v>-0.06491272243333959</v>
+        <v>-0.072219699572083</v>
       </c>
       <c r="AD4">
-        <v>2214.7</v>
+        <v>1853.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2214.7</v>
+        <v>1853.7</v>
       </c>
       <c r="AG4">
-        <v>1735.9</v>
+        <v>1412.5</v>
       </c>
       <c r="AH4">
-        <v>0.3533625847626645</v>
+        <v>0.3557760589601366</v>
       </c>
       <c r="AI4">
-        <v>0.45696894666254</v>
+        <v>0.4295944380069525</v>
       </c>
       <c r="AJ4">
-        <v>0.2998773472454955</v>
+        <v>0.2961774758340148</v>
       </c>
       <c r="AK4">
-        <v>0.3974403003869313</v>
+        <v>0.3646290464143735</v>
       </c>
       <c r="AL4">
-        <v>64.40000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="AM4">
-        <v>64.40000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="AN4">
-        <v>52.23349056603773</v>
+        <v>-398.6451612903226</v>
       </c>
       <c r="AO4">
-        <v>0.7391304347826086</v>
+        <v>0.02249589490968801</v>
       </c>
       <c r="AP4">
-        <v>40.94103773584906</v>
+        <v>-303.763440860215</v>
       </c>
       <c r="AQ4">
-        <v>0.7391304347826086</v>
+        <v>0.02249589490968801</v>
       </c>
     </row>
     <row r="5">
@@ -990,22 +990,22 @@
         </is>
       </c>
       <c r="G5">
-        <v>-1.071428571428571</v>
+        <v>-4.371681415929205</v>
       </c>
       <c r="H5">
-        <v>-1.071428571428571</v>
+        <v>-4.371681415929205</v>
       </c>
       <c r="I5">
-        <v>-2.545193499362894</v>
+        <v>-2.589307962222569</v>
       </c>
       <c r="J5">
-        <v>-2.545193499362894</v>
+        <v>-2.589307962222569</v>
       </c>
       <c r="K5">
-        <v>-5.04</v>
+        <v>-2.67</v>
       </c>
       <c r="L5">
-        <v>-2.4</v>
+        <v>-2.36283185840708</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1029,73 +1029,195 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>29</v>
+        <v>35.9</v>
       </c>
       <c r="V5">
-        <v>5.967078189300411</v>
+        <v>15.88495575221239</v>
       </c>
       <c r="W5">
-        <v>-0.2739130434782609</v>
+        <v>-0.07196765498652291</v>
       </c>
       <c r="X5">
-        <v>0.08651405583827518</v>
+        <v>0.07541939952265882</v>
       </c>
       <c r="Y5">
-        <v>-0.360427099316536</v>
+        <v>-0.1473870545091817</v>
       </c>
       <c r="Z5">
-        <v>2.610213975348184</v>
+        <v>0.1372260187628843</v>
       </c>
       <c r="AA5">
-        <v>-6.643499642002374</v>
+        <v>-0.3553204230068399</v>
       </c>
       <c r="AB5">
-        <v>0.08524263538609805</v>
+        <v>0.07376051793025186</v>
       </c>
       <c r="AC5">
-        <v>-6.728742277388473</v>
+        <v>-0.4290809409370917</v>
       </c>
       <c r="AD5">
         <v>0</v>
       </c>
       <c r="AE5">
-        <v>0.604531743310384</v>
+        <v>0.1345899865575085</v>
       </c>
       <c r="AF5">
-        <v>0.604531743310384</v>
+        <v>0.1345899865575085</v>
       </c>
       <c r="AG5">
-        <v>-28.39546825668961</v>
+        <v>-35.76541001344249</v>
       </c>
       <c r="AH5">
-        <v>0.1106282791842951</v>
+        <v>0.0562058587537137</v>
       </c>
       <c r="AI5">
-        <v>0.01603339745540379</v>
+        <v>0.003874811437520801</v>
       </c>
       <c r="AJ5">
-        <v>1.206496847523678</v>
+        <v>1.067451793578806</v>
       </c>
       <c r="AK5">
-        <v>-3.26214770582141</v>
+        <v>30.68912194069409</v>
       </c>
       <c r="AL5">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.388</v>
+        <v>-0.534</v>
       </c>
       <c r="AN5">
         <v>-0</v>
       </c>
-      <c r="AO5">
-        <v>-5670</v>
-      </c>
       <c r="AP5">
-        <v>5.446004652222787</v>
+        <v>12.29474390286782</v>
       </c>
       <c r="AQ5">
-        <v>14.61340206185567</v>
+        <v>5.599250936329588</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cheche Group Inc. (NasdaqCM:CCG)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>-0.0233264675592173</v>
+      </c>
+      <c r="H6">
+        <v>-0.04196704428424305</v>
+      </c>
+      <c r="I6">
+        <v>-0.04103114013387382</v>
+      </c>
+      <c r="J6">
+        <v>-0.04103114013387382</v>
+      </c>
+      <c r="K6">
+        <v>27.3</v>
+      </c>
+      <c r="L6">
+        <v>0.07028836251287333</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>-0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>16.7</v>
+      </c>
+      <c r="V6">
+        <v>0.034109477124183</v>
+      </c>
+      <c r="W6">
+        <v>-0.1725663716814159</v>
+      </c>
+      <c r="X6">
+        <v>0.07442950109284779</v>
+      </c>
+      <c r="Y6">
+        <v>-0.2469958727742637</v>
+      </c>
+      <c r="Z6">
+        <v>17.8718721806934</v>
+      </c>
+      <c r="AA6">
+        <v>-0.7333032919007122</v>
+      </c>
+      <c r="AB6">
+        <v>0.07381818912747125</v>
+      </c>
+      <c r="AC6">
+        <v>-0.8071214810281835</v>
+      </c>
+      <c r="AD6">
+        <v>8.69</v>
+      </c>
+      <c r="AE6">
+        <v>2.03247413998294</v>
+      </c>
+      <c r="AF6">
+        <v>10.72247413998294</v>
+      </c>
+      <c r="AG6">
+        <v>-5.97752586001706</v>
+      </c>
+      <c r="AH6">
+        <v>0.02143112631191328</v>
+      </c>
+      <c r="AI6">
+        <v>0.1984817302554282</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.01235990091371743</v>
+      </c>
+      <c r="AK6">
+        <v>-0.1601588854371644</v>
+      </c>
+      <c r="AL6">
+        <v>0.479</v>
+      </c>
+      <c r="AM6">
+        <v>0.205</v>
+      </c>
+      <c r="AN6">
+        <v>-0.5781769793745841</v>
+      </c>
+      <c r="AO6">
+        <v>-35.07306889352819</v>
+      </c>
+      <c r="AP6">
+        <v>0.3977063113783806</v>
+      </c>
+      <c r="AQ6">
+        <v>-81.95121951219514</v>
       </c>
     </row>
   </sheetData>
